--- a/MAJSushiConfig/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-body-structure-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-body-structure-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,7 +559,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-location-body-structure-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-location-body-structure-document|0.1.0</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -988,7 +988,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="32.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="88.46875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="85.265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
